--- a/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_capsule_tiny.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/anomaly/ANOMALY-raw-mvtec_capsule_tiny.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="padim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stfpm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uflow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,105 +478,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -589,116 +580,107 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>11.46592402458191</v>
+        <v>11.42530918121338</v>
       </c>
       <c r="D2" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0334753990173339</v>
+        <v>0.1876435875892639</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9310345053672791</v>
+        <v>0.9270386099815368</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9198312163352966</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9121338725090028</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3566694855690002</v>
+        <v>0.2745763957500458</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0679565519094467</v>
+        <v>0.0154942189804231</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0565277934074401</v>
+        <v>0.0554796180339774</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0178231639091414</v>
+        <v>0.0436170167393154</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0783267731618399</v>
+        <v>6.135710716247559</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0671666968952525</v>
+        <v>21.96992874145508</v>
       </c>
       <c r="O2" t="n">
-        <v>7.05797290802002</v>
-      </c>
-      <c r="P2" t="n">
-        <v>31.01740217208862</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>26.59801197052002</v>
+        <v>17.27233862876892</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-161535</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-153148</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -710,116 +692,107 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>11.57805013656616</v>
+        <v>11.18368077278137</v>
       </c>
       <c r="D3" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0337038040161132</v>
+        <v>0.1862184256315231</v>
       </c>
       <c r="F3" t="n">
         <v>0.9310345053672791</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9121338725090028</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9083333611488342</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3603918552398681</v>
+        <v>0.2738711237907409</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06888259202241891</v>
+        <v>0.0154883584590873</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0559649653732776</v>
+        <v>0.0558223947130068</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0176587676761126</v>
+        <v>0.0425289604398939</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07913709349102439</v>
+        <v>6.133389949798584</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0666131088227936</v>
+        <v>22.10566830635071</v>
       </c>
       <c r="O3" t="n">
-        <v>6.992871999740601</v>
-      </c>
-      <c r="P3" t="n">
-        <v>31.33828902244568</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>26.37879109382629</v>
+        <v>16.841468334198</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-161748</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-153345</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -831,116 +804,107 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>11.59447979927063</v>
+        <v>11.58165860176086</v>
       </c>
       <c r="D4" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0341377258300781</v>
+        <v>0.1864789277315139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9270386099815368</v>
+        <v>0.9310345053672791</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9198312163352966</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9045643210411072</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3568413257598877</v>
+        <v>0.2692981660366058</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0686999410390853</v>
+        <v>0.0152979950712184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0563414990901947</v>
+        <v>0.0554569664627614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0168049504058529</v>
+        <v>0.0438460147742069</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0791417023148199</v>
+        <v>6.058006048202515</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0671622662833242</v>
+        <v>21.96095871925354</v>
       </c>
       <c r="O4" t="n">
-        <v>6.654760360717773</v>
-      </c>
-      <c r="P4" t="n">
-        <v>31.3401141166687</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>26.59625744819641</v>
+        <v>17.36302185058594</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-162000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-153543</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -952,116 +916,107 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>11.7077784538269</v>
+        <v>11.48286271095276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0343310832977294</v>
+        <v>0.1885291785001754</v>
       </c>
       <c r="F5" t="n">
         <v>0.9310345053672791</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9356223344802856</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9344978332519532</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3602478206157684</v>
+        <v>0.2700299024581909</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06843330711126321</v>
+        <v>0.0152484449473294</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0554450452327728</v>
+        <v>0.0562673223139059</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0170246519223608</v>
+        <v>0.0438438786400689</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0789064066578643</v>
+        <v>6.038384199142456</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06566559124474571</v>
+        <v>22.28185963630676</v>
       </c>
       <c r="O5" t="n">
-        <v>6.741762161254883</v>
-      </c>
-      <c r="P5" t="n">
-        <v>31.24693703651428</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>26.00357413291931</v>
+        <v>17.36217594146729</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-162213</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-153741</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1073,116 +1028,107 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>11.45737171173096</v>
+        <v>11.20175909996033</v>
       </c>
       <c r="D6" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0332348346710205</v>
+        <v>0.1885897368192672</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9304347634315492</v>
+        <v>0.9264069199562072</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9396551847457886</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8815165758132935</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3589651584625244</v>
+        <v>0.2695449590682983</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06911181658506391</v>
+        <v>0.0153805968737361</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0553560778498649</v>
+        <v>0.0557871773989513</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0172036211900036</v>
+        <v>0.0431559567499642</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0795527786919565</v>
+        <v>6.090716361999512</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0656654654127178</v>
+        <v>22.09172224998474</v>
       </c>
       <c r="O6" t="n">
-        <v>6.812633991241455</v>
-      </c>
-      <c r="P6" t="n">
-        <v>31.50290036201477</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>26.00352430343628</v>
+        <v>17.08975887298584</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-162426</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-153938</t>
+          <t>padim</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>padim</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,105 +1194,95 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>export:test/iter_time</t>
+          <t>torch:test/latency</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/iter_time</t>
+          <t>export:test/latency</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/latency</t>
+          <t>optimize:test/latency</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>export:test/latency</t>
+          <t>torch:test/e2e_time</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/latency</t>
+          <t>export:test/e2e_time</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>torch:test/e2e_time</t>
+          <t>optimize:test/e2e_time</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>export:test/e2e_time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>optimize:test/e2e_time</t>
+          <t>task</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>model</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>task</t>
+          <t>data_group</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>data_group</t>
+          <t>otx_version</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>otx_ref</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otx_version</t>
+          <t>test_branch</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otx_ref</t>
+          <t>test_commit</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>test_branch</t>
+          <t>cpu_info</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>test_commit</t>
+          <t>accelerator_info</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>cpu_info</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>accelerator_info</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>user_name</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>machine_name</t>
         </is>
@@ -1357,119 +1293,110 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>35.05695199966431</v>
+        <v>512.304276227951</v>
       </c>
       <c r="D2" t="n">
-        <v>1.75</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0163010120391845</v>
+        <v>0.0239425934512506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9051724076271056</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9045643210411072</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1776645332574844</v>
+        <v>0.2478396892547607</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0605232901871204</v>
+        <v>0.0143971629817076</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0512394085526466</v>
+        <v>0.0454356128519231</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0114630695545312</v>
+        <v>0.0349634644961116</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0710822054834076</v>
+        <v>5.701276540756226</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0624470427782848</v>
+        <v>17.99250268936157</v>
       </c>
       <c r="O2" t="n">
-        <v>4.53937554359436</v>
-      </c>
-      <c r="P2" t="n">
-        <v>28.14855337142944</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>24.72902894020081</v>
+        <v>13.8455319404602</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250715-230723</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250529-165051</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1478,119 +1405,110 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>34.44559550285339</v>
+        <v>502.1794145107269</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799999952316284</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0184171199798583</v>
+        <v>0.0238870097393238</v>
       </c>
       <c r="F3" t="n">
         <v>0.9037656784057616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9045643210411072</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8608695864677429</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.282354474067688</v>
+        <v>0.2464335262775421</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0615953803062438</v>
+        <v>0.0144185604471148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0504315644502639</v>
+        <v>0.0458981683759978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0148891625982342</v>
+        <v>0.0351546364601212</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07386196622944841</v>
+        <v>5.709749937057495</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0623142225573761</v>
+        <v>18.17567467689514</v>
       </c>
       <c r="O3" t="n">
-        <v>5.896108388900757</v>
-      </c>
-      <c r="P3" t="n">
-        <v>29.24933862686157</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>24.67643213272095</v>
+        <v>13.92123603820801</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250715-231748</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250529-165304</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1599,119 +1517,110 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>35.47212910652161</v>
+        <v>520.0725038051605</v>
       </c>
       <c r="D4" t="n">
-        <v>1.769999980926514</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0177625656127929</v>
+        <v>0.023784422182611</v>
       </c>
       <c r="F4" t="n">
         <v>0.8999999761581421</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9045643210411072</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8898305296897888</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2047529518604278</v>
+        <v>0.2481556534767151</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0611687786877155</v>
+        <v>0.0143545257924783</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0517148226499557</v>
+        <v>0.0494637489318847</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0124591516725944</v>
+        <v>0.0389974382188585</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0726403353190181</v>
+        <v>5.684392213821411</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0635656256868381</v>
+        <v>19.58764457702637</v>
       </c>
       <c r="O4" t="n">
-        <v>4.933824062347412</v>
-      </c>
-      <c r="P4" t="n">
-        <v>28.76557278633118</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25.17198777198792</v>
+        <v>15.44298553466797</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250715-232803</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250529-165519</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1720,119 +1629,110 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="C5" t="n">
-        <v>34.8633759021759</v>
+        <v>505.2132813930512</v>
       </c>
       <c r="D5" t="n">
-        <v>1.799999952316284</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0192563533782958</v>
+        <v>0.0238878801120099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9075630307197572</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8999999761581421</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2405972480773925</v>
+        <v>0.2480608969926834</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0624011866748333</v>
+        <v>0.0144736736711829</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0508240908384323</v>
+        <v>0.0460558551730531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0135907946210919</v>
+        <v>0.0353762724182822</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07451666304559409</v>
+        <v>5.731574773788452</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0627112840161179</v>
+        <v>18.23811864852905</v>
       </c>
       <c r="O5" t="n">
-        <v>5.381954669952393</v>
-      </c>
-      <c r="P5" t="n">
-        <v>29.50859856605529</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>24.83366847038269</v>
+        <v>14.00900387763977</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250715-233839</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250529-165735</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ANOMALY</t>
+          <t>tiny</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
@@ -1841,119 +1741,826 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C6" t="n">
-        <v>35.57432150840759</v>
+        <v>538.4645833969116</v>
       </c>
       <c r="D6" t="n">
-        <v>1.769999980926514</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0182902336120605</v>
+        <v>0.023759354965697</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8999999761581421</v>
+        <v>0.9106382727622986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8999999761581421</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2144980430603027</v>
+        <v>0.2482306510210037</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0606220141053199</v>
+        <v>0.0151601548146719</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0518543384969234</v>
+        <v>0.0456188206720833</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0128381083710025</v>
+        <v>0.0350997875435183</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0723681576324231</v>
+        <v>6.003421306610107</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0638271503978305</v>
+        <v>18.06505298614502</v>
       </c>
       <c r="O6" t="n">
-        <v>5.083890914916992</v>
-      </c>
-      <c r="P6" t="n">
-        <v>28.65779042243957</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>25.27555155754089</v>
+        <v>13.89951586723328</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250715-234857</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250529-165950</t>
+          <t>stfpm</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mvtec_capsule_tiny</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>training:epoch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>training:e2e_time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>training:gpu_mem</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>training:train/iter_time</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/image_F1Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/iter_time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/latency</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/latency</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/latency</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>torch:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>export:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>optimize:test/e2e_time</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>task</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>data_group</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>otx_version</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>otx_ref</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>test_branch</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>test_commit</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>cpu_info</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>accelerator_info</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>user_name</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>machine_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>199</v>
+      </c>
+      <c r="C2" t="n">
+        <v>886.6186649799347</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.949999809265137</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0990212142617258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.91304349899292</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3246901929378509</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0189011759228176</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.08134841617911751</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07497676815649471</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7.484865665435791</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32.21397280693054</v>
+      </c>
+      <c r="O2" t="n">
+        <v>29.69080018997192</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>20250714-185857</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>ANOMALY</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mvtec_capsule_tiny</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>199</v>
+      </c>
+      <c r="C3" t="n">
+        <v>877.8447985649109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.09871422862587249</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9145299196243286</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3064631521701813</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0181852789840312</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07946607741442591</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.07341079398839161</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.201370477676392</v>
+      </c>
+      <c r="N3" t="n">
+        <v>31.46856665611267</v>
+      </c>
+      <c r="O3" t="n">
+        <v>29.07067441940308</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>20250714-191616</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mvtec_capsule_tiny</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>199</v>
+      </c>
+      <c r="C4" t="n">
+        <v>889.5359125137329</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.309999942779541</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0985585754016535</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9406392574310304</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3264199793338775</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0189557617360895</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0805806818634572</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.07467244430021799</v>
+      </c>
+      <c r="M4" t="n">
+        <v>7.506481647491455</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31.90995001792908</v>
+      </c>
+      <c r="O4" t="n">
+        <v>29.57028794288636</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20250714-193322</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mvtec_capsule_tiny</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>897.0860555171967</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.059999942779541</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0990614402458895</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9298245906829834</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3265646696090698</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0188242281326139</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.08260330467513111</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.075030738657171</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7.454394340515137</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32.71090865135193</v>
+      </c>
+      <c r="O5" t="n">
+        <v>29.71217250823974</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>20250714-195043</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mvtec_capsule_tiny</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2.5.0dev</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>HEAD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9b7168126</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>anonymous</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>199</v>
+      </c>
+      <c r="C6" t="n">
+        <v>895.6127254962921</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.059999942779541</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0989334906764964</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9411764740943908</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3210596144199371</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0187914949474912</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.07842948942473441</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0726898818305044</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.441431999206543</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31.05807781219482</v>
+      </c>
+      <c r="O6" t="n">
+        <v>28.78519320487976</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>20250714-200811</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ANOMALY</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>uflow</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>tiny</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>stfpm</t>
+          <t>mvtec_capsule_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>tiny</t>
+          <t>2.5.0dev</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>mvtec_capsule_tiny</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>HEAD</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>9b7168126</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>release/2.5</t>
+          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5a3348332</t>
+          <t>GPU 0: NVIDIA GeForce RTX 4090 (UUID: GPU-727b955d-c6ba-faf7-856c-39e827dbb80d)</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Intel(R) Core(TM) i9-10980XE CPU @ 3.00GHz</t>
+          <t>anonymous</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>GPU 0: NVIDIA GeForce RTX 3090 (UUID: GPU-33fa90f3-961d-bb69-cc71-20b2c645b763)
-GPU 1: NVIDIA GeForce RTX 3090 (UUID: GPU-904c43d6-060e-b707-c689-6455a4edd0c7)
-GPU 2: NVIDIA GeForce RTX 3090 (UUID: GPU-a9974426-be65-e280-195c-5a6760ab86e4)
-GPU 3: NVIDIA GeForce RTX 3090 (UUID: GPU-4d742c5a-39be-0118-b6d7-4fe0982543fc)</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>anonymous</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>workstation04</t>
+          <t>workstation</t>
         </is>
       </c>
     </row>
